--- a/diseases/d009/1995-1999.xlsx
+++ b/diseases/d009/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25958,7 +25958,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -29510,7 +29510,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -34246,7 +34246,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -35430,7 +35430,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -37243,7 +37243,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -38427,7 +38427,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -39611,7 +39611,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40795,7 +40795,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41979,7 +41979,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -43163,7 +43163,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -44347,7 +44347,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -45531,7 +45531,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46715,7 +46715,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -47899,7 +47899,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -49083,7 +49083,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -50267,7 +50267,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -52080,7 +52080,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -53264,7 +53264,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -54448,7 +54448,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -55632,7 +55632,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -56816,7 +56816,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -58000,7 +58000,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">
@@ -59184,7 +59184,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -60368,7 +60368,7 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN302" t="b">
@@ -61552,7 +61552,7 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN308" t="b">
@@ -62736,7 +62736,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -63920,7 +63920,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -65104,7 +65104,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">

--- a/diseases/d009/1995-1999.xlsx
+++ b/diseases/d009/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21543,6 +21543,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22406,7 +22411,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22966,6 +22971,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23590,7 +23600,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24150,6 +24160,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24774,7 +24789,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25334,6 +25349,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25958,7 +25978,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26518,6 +26538,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27142,7 +27167,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27702,6 +27727,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28326,7 +28356,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -28886,6 +28916,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29510,7 +29545,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -30070,6 +30105,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30694,7 +30734,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -31254,6 +31294,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31878,7 +31923,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -32438,6 +32483,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33062,7 +33112,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -33622,6 +33672,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34246,7 +34301,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -34806,6 +34861,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35430,7 +35490,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -36380,6 +36440,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37243,7 +37308,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37803,6 +37868,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38427,7 +38497,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38987,6 +39057,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39611,7 +39686,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40171,6 +40246,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40795,7 +40875,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41355,6 +41435,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41979,7 +42064,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -42539,6 +42624,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43163,7 +43253,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43723,6 +43813,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44347,7 +44442,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44907,6 +45002,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45531,7 +45631,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46091,6 +46191,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46715,7 +46820,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -47275,6 +47380,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47899,7 +48009,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48459,6 +48569,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49083,7 +49198,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -49643,6 +49758,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50267,7 +50387,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -51217,6 +51337,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52080,7 +52205,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -52640,6 +52765,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53264,7 +53394,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -53824,6 +53954,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54448,7 +54583,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -55008,6 +55143,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55632,7 +55772,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -56192,6 +56332,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56816,7 +56961,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -57376,6 +57521,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58000,7 +58150,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">
@@ -58560,6 +58710,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59184,7 +59339,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -59744,6 +59899,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60368,7 +60528,7 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN302" t="b">
@@ -60928,6 +61088,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61552,7 +61717,7 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN308" t="b">
@@ -62112,6 +62277,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62736,7 +62906,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -63296,6 +63466,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63920,7 +64095,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -64480,6 +64655,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65104,7 +65284,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">

--- a/diseases/d009/1995-1999.xlsx
+++ b/diseases/d009/1995-1999.xlsx
@@ -21538,6 +21538,11 @@
       <c r="Q106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21550,13 +21555,23 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22951,6 +22966,11 @@
       <c r="Q113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22963,13 +22983,23 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
       </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV113" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24125,6 +24155,11 @@
       <c r="Q119" t="n">
         <v>0</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24137,13 +24172,23 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
       </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV119" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25299,6 +25344,11 @@
       <c r="Q125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25311,13 +25361,23 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
       </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV125" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26473,6 +26533,11 @@
       <c r="Q131" t="n">
         <v>0</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26485,13 +26550,23 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
       </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV131" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27647,6 +27722,11 @@
       <c r="Q137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27659,13 +27739,23 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28821,6 +28911,11 @@
       <c r="Q143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28833,13 +28928,23 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
       </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV143" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29995,6 +30100,11 @@
       <c r="Q149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30007,13 +30117,23 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
       </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV149" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31169,6 +31289,11 @@
       <c r="Q155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31181,13 +31306,23 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
       </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV155" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32343,6 +32478,11 @@
       <c r="Q161" t="n">
         <v>0</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32355,13 +32495,23 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
       </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV161" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33517,6 +33667,11 @@
       <c r="Q167" t="n">
         <v>0</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33529,13 +33684,23 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
       </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV167" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34691,6 +34856,11 @@
       <c r="Q173" t="n">
         <v>0</v>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34703,13 +34873,23 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
       </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV173" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -36255,6 +36435,11 @@
       <c r="Q181" t="n">
         <v>0</v>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36267,13 +36452,23 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
       </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV181" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37668,6 +37863,11 @@
       <c r="Q188" t="n">
         <v>0</v>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37680,13 +37880,23 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
       </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV188" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38842,6 +39052,11 @@
       <c r="Q194" t="n">
         <v>0</v>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38854,13 +39069,23 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
       </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV194" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -40016,6 +40241,11 @@
       <c r="Q200" t="n">
         <v>0</v>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40028,13 +40258,23 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
       </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV200" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41190,6 +41430,11 @@
       <c r="Q206" t="n">
         <v>0</v>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41202,13 +41447,23 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
         <v>0</v>
       </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV206" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42364,6 +42619,11 @@
       <c r="Q212" t="n">
         <v>0</v>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42376,13 +42636,23 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
       </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV212" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43538,6 +43808,11 @@
       <c r="Q218" t="n">
         <v>0</v>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43550,13 +43825,23 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
       </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV218" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -44712,6 +44997,11 @@
       <c r="Q224" t="n">
         <v>0</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44724,13 +45014,23 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
       </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV224" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -45886,6 +46186,11 @@
       <c r="Q230" t="n">
         <v>0</v>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45898,13 +46203,23 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
       </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV230" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -47060,6 +47375,11 @@
       <c r="Q236" t="n">
         <v>0</v>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47072,13 +47392,23 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
         <v>0</v>
       </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV236" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48234,6 +48564,11 @@
       <c r="Q242" t="n">
         <v>0</v>
       </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48246,13 +48581,23 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
         <v>0</v>
       </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV242" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -49408,6 +49753,11 @@
       <c r="Q248" t="n">
         <v>0</v>
       </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49420,13 +49770,23 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
         <v>0</v>
       </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV248" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -50972,6 +51332,11 @@
       <c r="Q256" t="n">
         <v>0</v>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50984,13 +51349,23 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
         <v>0</v>
       </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV256" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -52385,6 +52760,11 @@
       <c r="Q263" t="n">
         <v>0</v>
       </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52397,13 +52777,23 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
         <v>0</v>
       </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV263" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -53559,6 +53949,11 @@
       <c r="Q269" t="n">
         <v>0</v>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53571,13 +53966,23 @@
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
         <v>0</v>
       </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV269" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -54733,6 +55138,11 @@
       <c r="Q275" t="n">
         <v>0</v>
       </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54745,13 +55155,23 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
         <v>0</v>
       </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV275" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -55907,6 +56327,11 @@
       <c r="Q281" t="n">
         <v>0</v>
       </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -55919,13 +56344,23 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr"/>
       <c r="AT281" t="n">
         <v>0</v>
       </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV281" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -57081,6 +57516,11 @@
       <c r="Q287" t="n">
         <v>0</v>
       </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57093,13 +57533,23 @@
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR287" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS287" t="inlineStr"/>
       <c r="AT287" t="n">
         <v>0</v>
       </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV287" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -58255,6 +58705,11 @@
       <c r="Q293" t="n">
         <v>0</v>
       </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA293" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58267,13 +58722,23 @@
       </c>
       <c r="AP293" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS293" t="inlineStr"/>
       <c r="AT293" t="n">
         <v>0</v>
       </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV293" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -59429,6 +59894,11 @@
       <c r="Q299" t="n">
         <v>0</v>
       </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -59441,13 +59911,23 @@
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr"/>
       <c r="AT299" t="n">
         <v>0</v>
       </c>
+      <c r="AU299" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV299" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -60603,6 +61083,11 @@
       <c r="Q305" t="n">
         <v>0</v>
       </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA305" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60615,13 +61100,23 @@
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR305" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS305" t="inlineStr"/>
       <c r="AT305" t="n">
         <v>0</v>
       </c>
+      <c r="AU305" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV305" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -61777,6 +62272,11 @@
       <c r="Q311" t="n">
         <v>0</v>
       </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA311" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61789,13 +62289,23 @@
       </c>
       <c r="AP311" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR311" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS311" t="inlineStr"/>
       <c r="AT311" t="n">
         <v>0</v>
       </c>
+      <c r="AU311" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV311" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -62951,6 +63461,11 @@
       <c r="Q317" t="n">
         <v>0</v>
       </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA317" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62963,13 +63478,23 @@
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS317" t="inlineStr"/>
       <c r="AT317" t="n">
         <v>0</v>
       </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV317" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -64125,6 +64650,11 @@
       <c r="Q323" t="n">
         <v>0</v>
       </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA323" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -64137,12 +64667,22 @@
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS323" t="inlineStr"/>
       <c r="AT323" t="n">
         <v>0</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
